--- a/datasets/sample_data/patients.xlsx
+++ b/datasets/sample_data/patients.xlsx
@@ -869,7 +869,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1971-05-08</t>
+          <t>1971-05-16</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -946,12 +946,12 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="Y2" t="n">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="BL2" t="n">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1978-07-09</t>
+          <t>1978-07-17</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="Y3" t="n">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="BL3" t="n">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1962-06-17</t>
+          <t>1962-06-25</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1606,12 +1606,12 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="Y4" t="n">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="BL4" t="n">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1995-05-27</t>
+          <t>1995-06-04</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="Y5" t="n">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="BL5" t="n">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1955-02-01</t>
+          <t>1955-02-09</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Y6" t="n">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="BL6" t="n">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1988-10-17</t>
+          <t>1988-10-25</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="Y7" t="n">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="BL7" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1968-06-07</t>
+          <t>1968-06-15</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="Y8" t="n">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="BL8" t="n">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1995-02-13</t>
+          <t>1995-02-21</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="Y9" t="n">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="BL9" t="n">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1988-11-24</t>
+          <t>1988-12-02</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="Y10" t="n">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="BL10" t="n">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1982-06-12</t>
+          <t>1982-06-20</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3904,12 +3904,12 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="Y11" t="n">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="BL11" t="n">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1987-10-15</t>
+          <t>1987-10-23</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="Y12" t="n">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="BL12" t="n">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1945-06-13</t>
+          <t>1945-06-21</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="Y13" t="n">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BK13" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="BL13" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1985-09-12</t>
+          <t>1985-09-20</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="Y14" t="n">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="BK14" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="BL14" t="n">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1992-01-17</t>
+          <t>1992-01-25</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="Y15" t="n">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="BK15" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="BL15" t="n">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1998-12-12</t>
+          <t>1998-12-20</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Y16" t="n">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="BK16" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="BL16" t="n">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1992-04-25</t>
+          <t>1992-05-03</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="Y17" t="n">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="BK17" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="BL17" t="n">
@@ -6137,7 +6137,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1960-08-06</t>
+          <t>1960-08-14</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="Y18" t="n">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="BK18" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="BL18" t="n">
@@ -6467,7 +6467,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1961-01-23</t>
+          <t>1961-01-31</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="Y19" t="n">
@@ -6700,7 +6700,7 @@
       </c>
       <c r="BK19" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="BL19" t="n">
@@ -6797,7 +6797,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1986-09-15</t>
+          <t>1986-09-23</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="Y20" t="n">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="BK20" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="BL20" t="n">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1985-07-23</t>
+          <t>1985-07-31</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -7204,12 +7204,12 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="Y21" t="n">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="BK21" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="BL21" t="n">
@@ -7457,7 +7457,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1981-11-27</t>
+          <t>1981-12-05</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="Y22" t="n">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="BK22" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="BL22" t="n">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1997-01-05</t>
+          <t>1997-01-13</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="Y23" t="n">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="BK23" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="BL23" t="n">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1945-12-25</t>
+          <t>1946-01-02</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="Y24" t="n">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="BK24" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="BL24" t="n">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1972-06-28</t>
+          <t>1972-07-06</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="Y25" t="n">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="BK25" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="BL25" t="n">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1947-05-26</t>
+          <t>1947-06-03</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -8850,12 +8850,12 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Y26" t="n">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="BK26" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="BL26" t="n">
@@ -9103,7 +9103,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1977-03-24</t>
+          <t>1977-04-01</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -9180,12 +9180,12 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="Y27" t="n">
@@ -9332,7 +9332,7 @@
       </c>
       <c r="BK27" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="BL27" t="n">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1962-11-07</t>
+          <t>1962-11-15</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Y28" t="n">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="BK28" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="BL28" t="n">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1966-04-25</t>
+          <t>1966-05-03</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -9836,12 +9836,12 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="Y29" t="n">
@@ -9988,7 +9988,7 @@
       </c>
       <c r="BK29" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="BL29" t="n">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1949-03-28</t>
+          <t>1949-04-05</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="Y30" t="n">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BK30" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="BL30" t="n">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1950-08-16</t>
+          <t>1950-08-24</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -10492,12 +10492,12 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="Y31" t="n">
@@ -10648,7 +10648,7 @@
       </c>
       <c r="BK31" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="BL31" t="n">
@@ -10745,7 +10745,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1990-01-16</t>
+          <t>1990-01-24</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -10822,12 +10822,12 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="Y32" t="n">
@@ -10978,7 +10978,7 @@
       </c>
       <c r="BK32" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="BL32" t="n">
@@ -11075,7 +11075,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1943-06-05</t>
+          <t>1943-06-13</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -11152,12 +11152,12 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="Y33" t="n">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="BK33" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="BL33" t="n">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1994-11-10</t>
+          <t>1994-11-18</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="Y34" t="n">
@@ -11638,7 +11638,7 @@
       </c>
       <c r="BK34" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="BL34" t="n">
@@ -11735,7 +11735,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1970-07-07</t>
+          <t>1970-07-15</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -11812,12 +11812,12 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="Y35" t="n">
@@ -11964,7 +11964,7 @@
       </c>
       <c r="BK35" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="BL35" t="n">
@@ -12061,7 +12061,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1943-04-10</t>
+          <t>1943-04-18</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -12138,12 +12138,12 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Y36" t="n">
@@ -12294,7 +12294,7 @@
       </c>
       <c r="BK36" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="BL36" t="n">
@@ -12391,7 +12391,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1969-09-01</t>
+          <t>1969-09-09</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -12468,12 +12468,12 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="Y37" t="n">
@@ -12620,7 +12620,7 @@
       </c>
       <c r="BK37" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="BL37" t="n">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1973-10-09</t>
+          <t>1973-10-17</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -12794,12 +12794,12 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="Y38" t="n">
@@ -12946,7 +12946,7 @@
       </c>
       <c r="BK38" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="BL38" t="n">
@@ -13043,7 +13043,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1999-02-21</t>
+          <t>1999-03-01</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -13120,12 +13120,12 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="Y39" t="n">
@@ -13272,7 +13272,7 @@
       </c>
       <c r="BK39" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="BL39" t="n">
@@ -13369,7 +13369,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1983-01-05</t>
+          <t>1983-01-13</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -13446,12 +13446,12 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-01-17</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="Y40" t="n">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="BK40" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="BL40" t="n">
@@ -13699,7 +13699,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1980-08-17</t>
+          <t>1980-08-25</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Y41" t="n">
@@ -13932,7 +13932,7 @@
       </c>
       <c r="BK41" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="BL41" t="n">
@@ -14029,7 +14029,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1997-12-09</t>
+          <t>1997-12-17</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -14106,12 +14106,12 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="Y42" t="n">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="BK42" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="BL42" t="n">
@@ -14359,7 +14359,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1957-03-17</t>
+          <t>1957-03-25</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -14436,12 +14436,12 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="Y43" t="n">
@@ -14592,7 +14592,7 @@
       </c>
       <c r="BK43" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="BL43" t="n">
@@ -14689,7 +14689,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1970-04-18</t>
+          <t>1970-04-26</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -14766,12 +14766,12 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Y44" t="n">
@@ -14922,7 +14922,7 @@
       </c>
       <c r="BK44" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="BL44" t="n">
@@ -15019,7 +15019,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1964-06-23</t>
+          <t>1964-07-01</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -15096,12 +15096,12 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="Y45" t="n">
@@ -15252,7 +15252,7 @@
       </c>
       <c r="BK45" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="BL45" t="n">
@@ -15349,7 +15349,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1964-08-31</t>
+          <t>1964-09-08</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -15426,12 +15426,12 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Y46" t="n">
@@ -15582,7 +15582,7 @@
       </c>
       <c r="BK46" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="BL46" t="n">
@@ -15679,7 +15679,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1978-01-01</t>
+          <t>1978-01-09</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -15756,12 +15756,12 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Y47" t="n">
@@ -15908,7 +15908,7 @@
       </c>
       <c r="BK47" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="BL47" t="n">
@@ -16005,7 +16005,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1990-05-15</t>
+          <t>1990-05-23</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -16082,12 +16082,12 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="Y48" t="n">
@@ -16238,7 +16238,7 @@
       </c>
       <c r="BK48" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="BL48" t="n">
@@ -16335,7 +16335,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1963-05-01</t>
+          <t>1963-05-09</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -16412,12 +16412,12 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="Y49" t="n">
@@ -16568,7 +16568,7 @@
       </c>
       <c r="BK49" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="BL49" t="n">
@@ -16665,7 +16665,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1948-07-25</t>
+          <t>1948-08-02</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -16742,12 +16742,12 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Y50" t="n">
@@ -16894,7 +16894,7 @@
       </c>
       <c r="BK50" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="BL50" t="n">
@@ -16991,7 +16991,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1992-08-07</t>
+          <t>1992-08-15</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -17068,12 +17068,12 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="Y51" t="n">
@@ -17224,7 +17224,7 @@
       </c>
       <c r="BK51" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="BL51" t="n">
@@ -17321,7 +17321,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1974-04-16</t>
+          <t>1974-04-24</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -17398,12 +17398,12 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="Y52" t="n">
@@ -17550,7 +17550,7 @@
       </c>
       <c r="BK52" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="BL52" t="n">
@@ -17647,7 +17647,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1999-06-16</t>
+          <t>1999-06-24</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -17724,12 +17724,12 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="Y53" t="n">
@@ -17880,7 +17880,7 @@
       </c>
       <c r="BK53" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="BL53" t="n">
@@ -17977,7 +17977,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1969-02-12</t>
+          <t>1969-02-20</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -18054,12 +18054,12 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="Y54" t="n">
@@ -18210,7 +18210,7 @@
       </c>
       <c r="BK54" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="BL54" t="n">
@@ -18307,7 +18307,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1973-08-25</t>
+          <t>1973-09-02</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -18384,12 +18384,12 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="Y55" t="n">
@@ -18540,7 +18540,7 @@
       </c>
       <c r="BK55" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="BL55" t="n">
@@ -18637,7 +18637,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1976-06-19</t>
+          <t>1976-06-27</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -18714,12 +18714,12 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="Y56" t="n">
@@ -18866,7 +18866,7 @@
       </c>
       <c r="BK56" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="BL56" t="n">
@@ -18963,7 +18963,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1972-06-05</t>
+          <t>1972-06-13</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -19040,12 +19040,12 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="Y57" t="n">
@@ -19196,7 +19196,7 @@
       </c>
       <c r="BK57" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="BL57" t="n">
@@ -19293,7 +19293,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1967-02-03</t>
+          <t>1967-02-11</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -19370,12 +19370,12 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="Y58" t="n">
@@ -19526,7 +19526,7 @@
       </c>
       <c r="BK58" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="BL58" t="n">
@@ -19623,7 +19623,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1956-06-05</t>
+          <t>1956-06-13</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -19700,12 +19700,12 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="Y59" t="n">
@@ -19856,7 +19856,7 @@
       </c>
       <c r="BK59" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="BL59" t="n">
@@ -19953,7 +19953,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1964-10-22</t>
+          <t>1964-10-30</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -20030,12 +20030,12 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="Y60" t="n">
@@ -20186,7 +20186,7 @@
       </c>
       <c r="BK60" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="BL60" t="n">
@@ -20283,7 +20283,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1944-08-05</t>
+          <t>1944-08-13</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -20360,12 +20360,12 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="Y61" t="n">
@@ -20512,7 +20512,7 @@
       </c>
       <c r="BK61" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="BL61" t="n">
@@ -20609,7 +20609,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1996-12-12</t>
+          <t>1996-12-20</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -20686,12 +20686,12 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="Y62" t="n">
@@ -20838,7 +20838,7 @@
       </c>
       <c r="BK62" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="BL62" t="n">
@@ -20935,7 +20935,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1964-11-26</t>
+          <t>1964-12-04</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -21012,12 +21012,12 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Y63" t="n">
@@ -21168,7 +21168,7 @@
       </c>
       <c r="BK63" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="BL63" t="n">
@@ -21265,7 +21265,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>1945-05-29</t>
+          <t>1945-06-06</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -21342,12 +21342,12 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="Y64" t="n">
@@ -21498,7 +21498,7 @@
       </c>
       <c r="BK64" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="BL64" t="n">
@@ -21595,7 +21595,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1991-02-14</t>
+          <t>1991-02-22</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -21672,12 +21672,12 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="Y65" t="n">
@@ -21828,7 +21828,7 @@
       </c>
       <c r="BK65" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="BL65" t="n">
@@ -21925,7 +21925,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1976-01-14</t>
+          <t>1976-01-22</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -22002,12 +22002,12 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Y66" t="n">
@@ -22158,7 +22158,7 @@
       </c>
       <c r="BK66" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="BL66" t="n">
@@ -22255,7 +22255,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>1982-05-06</t>
+          <t>1982-05-14</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -22332,12 +22332,12 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="Y67" t="n">
@@ -22488,7 +22488,7 @@
       </c>
       <c r="BK67" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-06-21</t>
         </is>
       </c>
       <c r="BL67" t="n">
@@ -22585,7 +22585,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1970-01-02</t>
+          <t>1970-01-10</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -22662,12 +22662,12 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="Y68" t="n">
@@ -22818,7 +22818,7 @@
       </c>
       <c r="BK68" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="BL68" t="n">
@@ -22915,7 +22915,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1975-11-10</t>
+          <t>1975-11-18</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -22992,12 +22992,12 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="Y69" t="n">
@@ -23148,7 +23148,7 @@
       </c>
       <c r="BK69" t="inlineStr">
         <is>
-          <t>2025-08-09</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="BL69" t="n">
@@ -23245,7 +23245,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1964-02-12</t>
+          <t>1964-02-20</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -23322,12 +23322,12 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="Y70" t="n">
@@ -23478,7 +23478,7 @@
       </c>
       <c r="BK70" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BL70" t="n">
@@ -23575,7 +23575,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1983-11-15</t>
+          <t>1983-11-23</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -23652,12 +23652,12 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="Y71" t="n">
@@ -23804,7 +23804,7 @@
       </c>
       <c r="BK71" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="BL71" t="n">
@@ -23901,7 +23901,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1956-06-17</t>
+          <t>1956-06-25</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -23978,12 +23978,12 @@
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="Y72" t="n">
@@ -24134,7 +24134,7 @@
       </c>
       <c r="BK72" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="BL72" t="n">
@@ -24231,7 +24231,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1975-08-26</t>
+          <t>1975-09-03</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -24308,12 +24308,12 @@
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="Y73" t="n">
@@ -24464,7 +24464,7 @@
       </c>
       <c r="BK73" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="BL73" t="n">
@@ -24561,7 +24561,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1999-12-09</t>
+          <t>1999-12-17</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -24638,12 +24638,12 @@
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="Y74" t="n">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="BK74" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="BL74" t="n">
@@ -24891,7 +24891,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2000-07-18</t>
+          <t>2000-07-26</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -24968,12 +24968,12 @@
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="Y75" t="n">
@@ -25120,7 +25120,7 @@
       </c>
       <c r="BK75" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="BL75" t="n">
@@ -25217,7 +25217,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1970-06-30</t>
+          <t>1970-07-08</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -25294,12 +25294,12 @@
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="Y76" t="n">
@@ -25446,7 +25446,7 @@
       </c>
       <c r="BK76" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="BL76" t="n">
@@ -25543,7 +25543,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>1960-06-18</t>
+          <t>1960-06-26</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -25620,12 +25620,12 @@
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Y77" t="n">
@@ -25776,7 +25776,7 @@
       </c>
       <c r="BK77" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="BL77" t="n">
@@ -25873,7 +25873,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>1993-12-12</t>
+          <t>1993-12-20</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -25950,12 +25950,12 @@
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="Y78" t="n">
@@ -26106,7 +26106,7 @@
       </c>
       <c r="BK78" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="BL78" t="n">
@@ -26203,7 +26203,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>1949-08-28</t>
+          <t>1949-09-05</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -26280,12 +26280,12 @@
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="Y79" t="n">
@@ -26432,7 +26432,7 @@
       </c>
       <c r="BK79" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2025-05-03</t>
         </is>
       </c>
       <c r="BL79" t="n">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1972-06-30</t>
+          <t>1972-07-08</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -26606,12 +26606,12 @@
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="Y80" t="n">
@@ -26762,7 +26762,7 @@
       </c>
       <c r="BK80" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="BL80" t="n">
@@ -26859,7 +26859,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1995-11-15</t>
+          <t>1995-11-23</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -26936,12 +26936,12 @@
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="Y81" t="n">
@@ -27088,7 +27088,7 @@
       </c>
       <c r="BK81" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="BL81" t="n">
@@ -27185,7 +27185,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1993-10-19</t>
+          <t>1993-10-27</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -27262,12 +27262,12 @@
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Y82" t="n">
@@ -27414,7 +27414,7 @@
       </c>
       <c r="BK82" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="BL82" t="n">
@@ -27511,7 +27511,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>1959-11-29</t>
+          <t>1959-12-07</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -27588,12 +27588,12 @@
       </c>
       <c r="W83" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="Y83" t="n">
@@ -27744,7 +27744,7 @@
       </c>
       <c r="BK83" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="BL83" t="n">
@@ -27841,7 +27841,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1952-05-05</t>
+          <t>1952-05-13</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -27918,12 +27918,12 @@
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="Y84" t="n">
@@ -28074,7 +28074,7 @@
       </c>
       <c r="BK84" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2025-08-16</t>
         </is>
       </c>
       <c r="BL84" t="n">
@@ -28171,7 +28171,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1957-08-21</t>
+          <t>1957-08-29</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -28248,12 +28248,12 @@
       </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="Y85" t="n">
@@ -28404,7 +28404,7 @@
       </c>
       <c r="BK85" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="BL85" t="n">
@@ -28501,7 +28501,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>1949-06-09</t>
+          <t>1949-06-17</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -28578,12 +28578,12 @@
       </c>
       <c r="W86" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="Y86" t="n">
@@ -28730,7 +28730,7 @@
       </c>
       <c r="BK86" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-07-12</t>
         </is>
       </c>
       <c r="BL86" t="n">
@@ -28827,7 +28827,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1958-04-14</t>
+          <t>1958-04-22</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -28904,12 +28904,12 @@
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="Y87" t="n">
@@ -29056,7 +29056,7 @@
       </c>
       <c r="BK87" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="BL87" t="n">
@@ -29153,7 +29153,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1997-05-03</t>
+          <t>1997-05-11</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -29230,12 +29230,12 @@
       </c>
       <c r="W88" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="Y88" t="n">
@@ -29386,7 +29386,7 @@
       </c>
       <c r="BK88" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="BL88" t="n">
@@ -29483,7 +29483,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>1976-07-04</t>
+          <t>1976-07-12</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -29560,12 +29560,12 @@
       </c>
       <c r="W89" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="Y89" t="n">
@@ -29716,7 +29716,7 @@
       </c>
       <c r="BK89" t="inlineStr">
         <is>
-          <t>2025-08-15</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="BL89" t="n">
@@ -29813,7 +29813,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1989-06-18</t>
+          <t>1989-06-26</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -29890,12 +29890,12 @@
       </c>
       <c r="W90" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Y90" t="n">
@@ -30046,7 +30046,7 @@
       </c>
       <c r="BK90" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="BL90" t="n">
@@ -30143,7 +30143,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1994-09-16</t>
+          <t>1994-09-24</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -30220,12 +30220,12 @@
       </c>
       <c r="W91" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="Y91" t="n">
@@ -30376,7 +30376,7 @@
       </c>
       <c r="BK91" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="BL91" t="n">
@@ -30473,7 +30473,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2000-11-04</t>
+          <t>2000-11-12</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -30550,12 +30550,12 @@
       </c>
       <c r="W92" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="Y92" t="n">
@@ -30702,7 +30702,7 @@
       </c>
       <c r="BK92" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="BL92" t="n">
@@ -30799,7 +30799,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>1975-06-29</t>
+          <t>1975-07-07</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -30876,12 +30876,12 @@
       </c>
       <c r="W93" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="Y93" t="n">
@@ -31032,7 +31032,7 @@
       </c>
       <c r="BK93" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="BL93" t="n">
@@ -31129,7 +31129,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>1962-12-11</t>
+          <t>1962-12-19</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -31206,12 +31206,12 @@
       </c>
       <c r="W94" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="Y94" t="n">
@@ -31358,7 +31358,7 @@
       </c>
       <c r="BK94" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="BL94" t="n">
@@ -31455,7 +31455,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>1969-09-24</t>
+          <t>1969-10-02</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -31532,12 +31532,12 @@
       </c>
       <c r="W95" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="Y95" t="n">
@@ -31688,7 +31688,7 @@
       </c>
       <c r="BK95" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="BL95" t="n">
@@ -31785,7 +31785,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>1960-03-21</t>
+          <t>1960-03-29</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -31862,12 +31862,12 @@
       </c>
       <c r="W96" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="Y96" t="n">
@@ -32018,7 +32018,7 @@
       </c>
       <c r="BK96" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BL96" t="n">
@@ -32115,7 +32115,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>1965-01-22</t>
+          <t>1965-01-30</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -32192,12 +32192,12 @@
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="Y97" t="n">
@@ -32344,7 +32344,7 @@
       </c>
       <c r="BK97" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="BL97" t="n">
@@ -32441,7 +32441,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>1940-12-09</t>
+          <t>1940-12-17</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -32518,12 +32518,12 @@
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="Y98" t="n">
@@ -32670,7 +32670,7 @@
       </c>
       <c r="BK98" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="BL98" t="n">
@@ -32767,7 +32767,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1990-07-29</t>
+          <t>1990-08-06</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -32844,12 +32844,12 @@
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="Y99" t="n">
@@ -33000,7 +33000,7 @@
       </c>
       <c r="BK99" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="BL99" t="n">
@@ -33097,7 +33097,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>1971-02-01</t>
+          <t>1971-02-09</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -33174,12 +33174,12 @@
       </c>
       <c r="W100" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="Y100" t="n">
@@ -33330,7 +33330,7 @@
       </c>
       <c r="BK100" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="BL100" t="n">
@@ -33427,7 +33427,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>1947-12-03</t>
+          <t>1947-12-11</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -33504,12 +33504,12 @@
       </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="Y101" t="n">
@@ -33660,7 +33660,7 @@
       </c>
       <c r="BK101" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="BL101" t="n">
@@ -33757,7 +33757,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>1980-12-15</t>
+          <t>1980-12-23</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -33834,12 +33834,12 @@
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="Y102" t="n">
@@ -33990,7 +33990,7 @@
       </c>
       <c r="BK102" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="BL102" t="n">
@@ -34087,7 +34087,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>1948-11-05</t>
+          <t>1948-11-13</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -34164,12 +34164,12 @@
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="Y103" t="n">
@@ -34320,7 +34320,7 @@
       </c>
       <c r="BK103" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="BL103" t="n">
@@ -34417,7 +34417,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>1949-07-17</t>
+          <t>1949-07-25</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -34494,12 +34494,12 @@
       </c>
       <c r="W104" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="Y104" t="n">
@@ -34650,7 +34650,7 @@
       </c>
       <c r="BK104" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="BL104" t="n">
@@ -34747,7 +34747,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>1980-09-20</t>
+          <t>1980-09-28</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -34824,12 +34824,12 @@
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="Y105" t="n">
@@ -34976,7 +34976,7 @@
       </c>
       <c r="BK105" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="BL105" t="n">
@@ -35073,7 +35073,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>1989-12-21</t>
+          <t>1989-12-29</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -35150,12 +35150,12 @@
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="Y106" t="n">
@@ -35306,7 +35306,7 @@
       </c>
       <c r="BK106" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="BL106" t="n">
@@ -35403,7 +35403,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>1958-02-01</t>
+          <t>1958-02-09</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -35480,12 +35480,12 @@
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="Y107" t="n">
@@ -35636,7 +35636,7 @@
       </c>
       <c r="BK107" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="BL107" t="n">
@@ -35733,7 +35733,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>1969-12-17</t>
+          <t>1969-12-25</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -35810,12 +35810,12 @@
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="Y108" t="n">
@@ -35966,7 +35966,7 @@
       </c>
       <c r="BK108" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="BL108" t="n">
@@ -36063,7 +36063,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>1965-02-09</t>
+          <t>1965-02-17</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -36140,12 +36140,12 @@
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="Y109" t="n">
@@ -36296,7 +36296,7 @@
       </c>
       <c r="BK109" t="inlineStr">
         <is>
-          <t>2025-09-27</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="BL109" t="n">
@@ -36393,7 +36393,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>1956-03-26</t>
+          <t>1956-04-03</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -36470,12 +36470,12 @@
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="Y110" t="n">
@@ -36622,7 +36622,7 @@
       </c>
       <c r="BK110" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="BL110" t="n">
@@ -36719,7 +36719,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>1975-05-07</t>
+          <t>1975-05-15</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -36796,12 +36796,12 @@
       </c>
       <c r="W111" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="Y111" t="n">
@@ -36952,7 +36952,7 @@
       </c>
       <c r="BK111" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="BL111" t="n">
@@ -37049,7 +37049,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>1951-02-25</t>
+          <t>1951-03-05</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -37126,12 +37126,12 @@
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="Y112" t="n">
@@ -37282,7 +37282,7 @@
       </c>
       <c r="BK112" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="BL112" t="n">
@@ -37379,7 +37379,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>1983-10-04</t>
+          <t>1983-10-12</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -37456,12 +37456,12 @@
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="Y113" t="n">
@@ -37612,7 +37612,7 @@
       </c>
       <c r="BK113" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="BL113" t="n">
@@ -37709,7 +37709,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>1993-12-26</t>
+          <t>1994-01-03</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -37786,12 +37786,12 @@
       </c>
       <c r="W114" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Y114" t="n">
@@ -37942,7 +37942,7 @@
       </c>
       <c r="BK114" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="BL114" t="n">
@@ -38039,7 +38039,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>1964-03-27</t>
+          <t>1964-04-04</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -38116,12 +38116,12 @@
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="Y115" t="n">
@@ -38272,7 +38272,7 @@
       </c>
       <c r="BK115" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="BL115" t="n">
@@ -38369,7 +38369,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>1989-08-31</t>
+          <t>1989-09-08</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -38446,12 +38446,12 @@
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Y116" t="n">
@@ -38598,7 +38598,7 @@
       </c>
       <c r="BK116" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="BL116" t="n">
@@ -38695,7 +38695,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>1954-04-20</t>
+          <t>1954-04-28</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -38772,12 +38772,12 @@
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="Y117" t="n">
@@ -38928,7 +38928,7 @@
       </c>
       <c r="BK117" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="BL117" t="n">
@@ -39025,7 +39025,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>1945-03-29</t>
+          <t>1945-04-06</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -39102,12 +39102,12 @@
       </c>
       <c r="W118" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="Y118" t="n">
@@ -39254,7 +39254,7 @@
       </c>
       <c r="BK118" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="BL118" t="n">
@@ -39351,7 +39351,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>1984-05-07</t>
+          <t>1984-05-15</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -39428,12 +39428,12 @@
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="Y119" t="n">
@@ -39584,7 +39584,7 @@
       </c>
       <c r="BK119" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="BL119" t="n">
@@ -39681,7 +39681,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>1973-07-10</t>
+          <t>1973-07-18</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -39758,12 +39758,12 @@
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="Y120" t="n">
@@ -39910,7 +39910,7 @@
       </c>
       <c r="BK120" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="BL120" t="n">
@@ -40007,7 +40007,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>1945-12-23</t>
+          <t>1945-12-31</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -40084,12 +40084,12 @@
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="Y121" t="n">
@@ -40240,7 +40240,7 @@
       </c>
       <c r="BK121" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="BL121" t="n">
@@ -40337,7 +40337,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>1956-11-27</t>
+          <t>1956-12-05</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -40414,12 +40414,12 @@
       </c>
       <c r="W122" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Y122" t="n">
@@ -40566,7 +40566,7 @@
       </c>
       <c r="BK122" t="inlineStr">
         <is>
-          <t>2025-05-03</t>
+          <t>2025-05-11</t>
         </is>
       </c>
       <c r="BL122" t="n">
@@ -40663,7 +40663,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>1976-07-04</t>
+          <t>1976-07-12</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -40740,12 +40740,12 @@
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Y123" t="n">
@@ -40896,7 +40896,7 @@
       </c>
       <c r="BK123" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="BL123" t="n">
@@ -40993,7 +40993,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>1997-08-24</t>
+          <t>1997-09-01</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -41070,12 +41070,12 @@
       </c>
       <c r="W124" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="Y124" t="n">
@@ -41222,7 +41222,7 @@
       </c>
       <c r="BK124" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="BL124" t="n">
@@ -41319,7 +41319,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>1995-03-02</t>
+          <t>1995-03-10</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -41396,12 +41396,12 @@
       </c>
       <c r="W125" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Y125" t="n">
@@ -41548,7 +41548,7 @@
       </c>
       <c r="BK125" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="BL125" t="n">
@@ -41645,7 +41645,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>1970-01-01</t>
+          <t>1970-01-09</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -41722,12 +41722,12 @@
       </c>
       <c r="W126" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="Y126" t="n">
@@ -41878,7 +41878,7 @@
       </c>
       <c r="BK126" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="BL126" t="n">
@@ -41975,7 +41975,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>1940-12-24</t>
+          <t>1941-01-01</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -42052,12 +42052,12 @@
       </c>
       <c r="W127" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Y127" t="n">
@@ -42204,7 +42204,7 @@
       </c>
       <c r="BK127" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="BL127" t="n">
@@ -42301,7 +42301,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>1988-08-13</t>
+          <t>1988-08-21</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -42378,12 +42378,12 @@
       </c>
       <c r="W128" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="Y128" t="n">
@@ -42530,7 +42530,7 @@
       </c>
       <c r="BK128" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="BL128" t="n">
@@ -42627,7 +42627,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>1970-06-24</t>
+          <t>1970-07-02</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -42704,12 +42704,12 @@
       </c>
       <c r="W129" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Y129" t="n">
@@ -42860,7 +42860,7 @@
       </c>
       <c r="BK129" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="BL129" t="n">
@@ -42957,7 +42957,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>1997-03-26</t>
+          <t>1997-04-03</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -43034,12 +43034,12 @@
       </c>
       <c r="W130" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="Y130" t="n">
@@ -43190,7 +43190,7 @@
       </c>
       <c r="BK130" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BL130" t="n">
@@ -43287,7 +43287,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>1958-07-26</t>
+          <t>1958-08-03</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -43364,12 +43364,12 @@
       </c>
       <c r="W131" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="Y131" t="n">
@@ -43516,7 +43516,7 @@
       </c>
       <c r="BK131" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="BL131" t="n">
@@ -43613,7 +43613,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>1996-10-15</t>
+          <t>1996-10-23</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -43690,12 +43690,12 @@
       </c>
       <c r="W132" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Y132" t="n">
@@ -43842,7 +43842,7 @@
       </c>
       <c r="BK132" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="BL132" t="n">
@@ -43939,7 +43939,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>1994-11-30</t>
+          <t>1994-12-08</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -44016,12 +44016,12 @@
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Y133" t="n">
@@ -44168,7 +44168,7 @@
       </c>
       <c r="BK133" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="BL133" t="n">
@@ -44265,7 +44265,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>1997-03-13</t>
+          <t>1997-03-21</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -44342,12 +44342,12 @@
       </c>
       <c r="W134" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="Y134" t="n">
@@ -44498,7 +44498,7 @@
       </c>
       <c r="BK134" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="BL134" t="n">
@@ -44595,7 +44595,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>1961-08-21</t>
+          <t>1961-08-29</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -44672,12 +44672,12 @@
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="Y135" t="n">
@@ -44828,7 +44828,7 @@
       </c>
       <c r="BK135" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="BL135" t="n">
@@ -44925,7 +44925,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>1963-04-02</t>
+          <t>1963-04-10</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -45002,12 +45002,12 @@
       </c>
       <c r="W136" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="Y136" t="n">
@@ -45158,7 +45158,7 @@
       </c>
       <c r="BK136" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-17</t>
         </is>
       </c>
       <c r="BL136" t="n">
@@ -45255,7 +45255,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>1949-01-20</t>
+          <t>1949-01-28</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -45332,12 +45332,12 @@
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="Y137" t="n">
@@ -45484,7 +45484,7 @@
       </c>
       <c r="BK137" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="BL137" t="n">
@@ -45581,7 +45581,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>1950-06-13</t>
+          <t>1950-06-21</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -45658,12 +45658,12 @@
       </c>
       <c r="W138" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="X138" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="Y138" t="n">
@@ -45814,7 +45814,7 @@
       </c>
       <c r="BK138" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="BL138" t="n">
@@ -45911,7 +45911,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>1974-10-11</t>
+          <t>1974-10-19</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -45988,12 +45988,12 @@
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="X139" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Y139" t="n">
@@ -46140,7 +46140,7 @@
       </c>
       <c r="BK139" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="BL139" t="n">
@@ -46237,7 +46237,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>1993-02-05</t>
+          <t>1993-02-13</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -46314,12 +46314,12 @@
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="Y140" t="n">
@@ -46470,7 +46470,7 @@
       </c>
       <c r="BK140" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="BL140" t="n">
@@ -46567,7 +46567,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>1992-05-02</t>
+          <t>1992-05-10</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -46644,12 +46644,12 @@
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="X141" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="Y141" t="n">
@@ -46800,7 +46800,7 @@
       </c>
       <c r="BK141" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="BL141" t="n">
@@ -46897,7 +46897,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>1992-05-03</t>
+          <t>1992-05-11</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -46974,12 +46974,12 @@
       </c>
       <c r="W142" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="Y142" t="n">
@@ -47126,7 +47126,7 @@
       </c>
       <c r="BK142" t="inlineStr">
         <is>
-          <t>2025-06-27</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="BL142" t="n">
@@ -47223,7 +47223,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>1941-10-07</t>
+          <t>1941-10-15</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -47300,12 +47300,12 @@
       </c>
       <c r="W143" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="Y143" t="n">
@@ -47452,7 +47452,7 @@
       </c>
       <c r="BK143" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="BL143" t="n">
@@ -47549,7 +47549,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>1976-11-03</t>
+          <t>1976-11-11</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -47626,12 +47626,12 @@
       </c>
       <c r="W144" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="X144" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="Y144" t="n">
@@ -47778,7 +47778,7 @@
       </c>
       <c r="BK144" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BL144" t="n">
@@ -47875,7 +47875,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>1977-02-07</t>
+          <t>1977-02-15</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -47952,12 +47952,12 @@
       </c>
       <c r="W145" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="X145" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="Y145" t="n">
@@ -48108,7 +48108,7 @@
       </c>
       <c r="BK145" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="BL145" t="n">
@@ -48205,7 +48205,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>1975-03-30</t>
+          <t>1975-04-07</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -48282,12 +48282,12 @@
       </c>
       <c r="W146" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="Y146" t="n">
@@ -48438,7 +48438,7 @@
       </c>
       <c r="BK146" t="inlineStr">
         <is>
-          <t>2025-05-17</t>
+          <t>2025-05-25</t>
         </is>
       </c>
       <c r="BL146" t="n">
@@ -48535,7 +48535,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>1995-01-17</t>
+          <t>1995-01-25</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -48612,12 +48612,12 @@
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="Y147" t="n">
@@ -48764,7 +48764,7 @@
       </c>
       <c r="BK147" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="BL147" t="n">
@@ -48861,7 +48861,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>1966-01-06</t>
+          <t>1966-01-14</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -48938,12 +48938,12 @@
       </c>
       <c r="W148" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="X148" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="Y148" t="n">
@@ -49090,7 +49090,7 @@
       </c>
       <c r="BK148" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="BL148" t="n">
@@ -49187,7 +49187,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>1974-04-14</t>
+          <t>1974-04-22</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -49264,12 +49264,12 @@
       </c>
       <c r="W149" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="Y149" t="n">
@@ -49416,7 +49416,7 @@
       </c>
       <c r="BK149" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="BL149" t="n">
@@ -49513,7 +49513,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>1954-07-05</t>
+          <t>1954-07-13</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -49590,12 +49590,12 @@
       </c>
       <c r="W150" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="X150" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-07</t>
         </is>
       </c>
       <c r="Y150" t="n">
@@ -49746,7 +49746,7 @@
       </c>
       <c r="BK150" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="BL150" t="n">
@@ -49843,7 +49843,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>1966-05-06</t>
+          <t>1966-05-14</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -49920,12 +49920,12 @@
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="X151" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="Y151" t="n">
@@ -50076,7 +50076,7 @@
       </c>
       <c r="BK151" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="BL151" t="n">
@@ -50173,7 +50173,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>1968-06-16</t>
+          <t>1968-06-24</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -50250,12 +50250,12 @@
       </c>
       <c r="W152" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="Y152" t="n">
@@ -50402,7 +50402,7 @@
       </c>
       <c r="BK152" t="inlineStr">
         <is>
-          <t>2025-05-24</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="BL152" t="n">
@@ -50499,7 +50499,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>1976-11-28</t>
+          <t>1976-12-06</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -50576,12 +50576,12 @@
       </c>
       <c r="W153" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="X153" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="Y153" t="n">
@@ -50732,7 +50732,7 @@
       </c>
       <c r="BK153" t="inlineStr">
         <is>
-          <t>2025-05-12</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="BL153" t="n">
@@ -50829,7 +50829,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>1951-03-07</t>
+          <t>1951-03-15</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -50906,12 +50906,12 @@
       </c>
       <c r="W154" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="X154" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="Y154" t="n">
@@ -51062,7 +51062,7 @@
       </c>
       <c r="BK154" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="BL154" t="n">
@@ -51159,7 +51159,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>1948-01-23</t>
+          <t>1948-01-31</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -51236,12 +51236,12 @@
       </c>
       <c r="W155" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="X155" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="Y155" t="n">
@@ -51392,7 +51392,7 @@
       </c>
       <c r="BK155" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="BL155" t="n">
@@ -51489,7 +51489,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>1953-07-18</t>
+          <t>1953-07-26</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -51566,12 +51566,12 @@
       </c>
       <c r="W156" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="X156" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="Y156" t="n">
@@ -51722,7 +51722,7 @@
       </c>
       <c r="BK156" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="BL156" t="n">
@@ -51819,7 +51819,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>1987-01-03</t>
+          <t>1987-01-11</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -51896,12 +51896,12 @@
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="X157" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="Y157" t="n">
@@ -52048,7 +52048,7 @@
       </c>
       <c r="BK157" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="BL157" t="n">
@@ -52145,7 +52145,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>1977-06-02</t>
+          <t>1977-06-10</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -52222,12 +52222,12 @@
       </c>
       <c r="W158" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="X158" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Y158" t="n">
@@ -52374,7 +52374,7 @@
       </c>
       <c r="BK158" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="BL158" t="n">
@@ -52471,7 +52471,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>1972-02-04</t>
+          <t>1972-02-12</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -52548,12 +52548,12 @@
       </c>
       <c r="W159" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="X159" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="Y159" t="n">
@@ -52704,7 +52704,7 @@
       </c>
       <c r="BK159" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="BL159" t="n">
@@ -52801,7 +52801,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>1960-10-23</t>
+          <t>1960-10-31</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -52878,12 +52878,12 @@
       </c>
       <c r="W160" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="X160" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Y160" t="n">
@@ -53030,7 +53030,7 @@
       </c>
       <c r="BK160" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="BL160" t="n">
@@ -53127,7 +53127,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>1942-03-14</t>
+          <t>1942-03-22</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -53204,12 +53204,12 @@
       </c>
       <c r="W161" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="X161" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="Y161" t="n">
@@ -53356,7 +53356,7 @@
       </c>
       <c r="BK161" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="BL161" t="n">
@@ -53453,7 +53453,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>1950-10-18</t>
+          <t>1950-10-26</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -53530,12 +53530,12 @@
       </c>
       <c r="W162" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="X162" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="Y162" t="n">
@@ -53682,7 +53682,7 @@
       </c>
       <c r="BK162" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="BL162" t="n">
@@ -53779,7 +53779,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>1952-06-25</t>
+          <t>1952-07-03</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -53856,12 +53856,12 @@
       </c>
       <c r="W163" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="X163" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="Y163" t="n">
@@ -54012,7 +54012,7 @@
       </c>
       <c r="BK163" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="BL163" t="n">
@@ -54109,7 +54109,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>1963-10-07</t>
+          <t>1963-10-15</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -54186,12 +54186,12 @@
       </c>
       <c r="W164" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="X164" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="Y164" t="n">
@@ -54342,7 +54342,7 @@
       </c>
       <c r="BK164" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BL164" t="n">
@@ -54439,7 +54439,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>1976-05-27</t>
+          <t>1976-06-04</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -54516,12 +54516,12 @@
       </c>
       <c r="W165" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="X165" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="Y165" t="n">
@@ -54668,7 +54668,7 @@
       </c>
       <c r="BK165" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="BL165" t="n">
@@ -54765,7 +54765,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>1964-12-01</t>
+          <t>1964-12-09</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -54842,12 +54842,12 @@
       </c>
       <c r="W166" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="X166" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="Y166" t="n">
@@ -54998,7 +54998,7 @@
       </c>
       <c r="BK166" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="BL166" t="n">
@@ -55095,7 +55095,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>1943-05-11</t>
+          <t>1943-05-19</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -55172,12 +55172,12 @@
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="X167" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="Y167" t="n">
@@ -55328,7 +55328,7 @@
       </c>
       <c r="BK167" t="inlineStr">
         <is>
-          <t>2025-09-07</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="BL167" t="n">
@@ -55425,7 +55425,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>1954-10-15</t>
+          <t>1954-10-23</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -55502,12 +55502,12 @@
       </c>
       <c r="W168" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="X168" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="Y168" t="n">
@@ -55654,7 +55654,7 @@
       </c>
       <c r="BK168" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="BL168" t="n">
@@ -55751,7 +55751,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>1963-07-27</t>
+          <t>1963-08-04</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -55828,12 +55828,12 @@
       </c>
       <c r="W169" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="X169" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="Y169" t="n">
@@ -55984,7 +55984,7 @@
       </c>
       <c r="BK169" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-08</t>
         </is>
       </c>
       <c r="BL169" t="n">
@@ -56081,7 +56081,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>1951-09-23</t>
+          <t>1951-10-01</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -56158,12 +56158,12 @@
       </c>
       <c r="W170" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="X170" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="Y170" t="n">
@@ -56314,7 +56314,7 @@
       </c>
       <c r="BK170" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="BL170" t="n">
@@ -56411,7 +56411,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>1998-01-18</t>
+          <t>1998-01-26</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -56488,12 +56488,12 @@
       </c>
       <c r="W171" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="X171" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="Y171" t="n">
@@ -56640,7 +56640,7 @@
       </c>
       <c r="BK171" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="BL171" t="n">
@@ -56737,7 +56737,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>1987-08-24</t>
+          <t>1987-09-01</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -56814,12 +56814,12 @@
       </c>
       <c r="W172" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="X172" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="Y172" t="n">
@@ -56970,7 +56970,7 @@
       </c>
       <c r="BK172" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="BL172" t="n">
@@ -57067,7 +57067,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>1990-03-18</t>
+          <t>1990-03-26</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -57144,12 +57144,12 @@
       </c>
       <c r="W173" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="X173" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="Y173" t="n">
@@ -57296,7 +57296,7 @@
       </c>
       <c r="BK173" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="BL173" t="n">
@@ -57393,7 +57393,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>1990-09-05</t>
+          <t>1990-09-13</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -57470,12 +57470,12 @@
       </c>
       <c r="W174" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="X174" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Y174" t="n">
@@ -57626,7 +57626,7 @@
       </c>
       <c r="BK174" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
+          <t>2025-09-07</t>
         </is>
       </c>
       <c r="BL174" t="n">
@@ -57723,7 +57723,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>1987-10-10</t>
+          <t>1987-10-18</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -57800,12 +57800,12 @@
       </c>
       <c r="W175" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="X175" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="Y175" t="n">
@@ -57952,7 +57952,7 @@
       </c>
       <c r="BK175" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="BL175" t="n">
@@ -58049,7 +58049,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>1941-12-29</t>
+          <t>1942-01-06</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -58126,12 +58126,12 @@
       </c>
       <c r="W176" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="X176" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="Y176" t="n">
@@ -58278,7 +58278,7 @@
       </c>
       <c r="BK176" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="BL176" t="n">
@@ -58375,7 +58375,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>1965-05-28</t>
+          <t>1965-06-05</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -58452,12 +58452,12 @@
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="X177" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="Y177" t="n">
@@ -58608,7 +58608,7 @@
       </c>
       <c r="BK177" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="BL177" t="n">
@@ -58705,7 +58705,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>1992-07-22</t>
+          <t>1992-07-30</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -58782,12 +58782,12 @@
       </c>
       <c r="W178" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="X178" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="Y178" t="n">
@@ -58938,7 +58938,7 @@
       </c>
       <c r="BK178" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="BL178" t="n">
@@ -59035,7 +59035,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>1969-11-20</t>
+          <t>1969-11-28</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -59112,12 +59112,12 @@
       </c>
       <c r="W179" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="X179" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="Y179" t="n">
@@ -59264,7 +59264,7 @@
       </c>
       <c r="BK179" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="BL179" t="n">
@@ -59361,7 +59361,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>1968-07-02</t>
+          <t>1968-07-10</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -59438,12 +59438,12 @@
       </c>
       <c r="W180" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="X180" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Y180" t="n">
@@ -59594,7 +59594,7 @@
       </c>
       <c r="BK180" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="BL180" t="n">
@@ -59691,7 +59691,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>1982-01-30</t>
+          <t>1982-02-07</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -59768,12 +59768,12 @@
       </c>
       <c r="W181" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="X181" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Y181" t="n">
@@ -59924,7 +59924,7 @@
       </c>
       <c r="BK181" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="BL181" t="n">
@@ -60021,7 +60021,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>1952-02-19</t>
+          <t>1952-02-27</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -60098,12 +60098,12 @@
       </c>
       <c r="W182" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="X182" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="Y182" t="n">
@@ -60250,7 +60250,7 @@
       </c>
       <c r="BK182" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2025-05-18</t>
         </is>
       </c>
       <c r="BL182" t="n">
@@ -60347,7 +60347,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>1955-05-19</t>
+          <t>1955-05-27</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -60424,12 +60424,12 @@
       </c>
       <c r="W183" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="X183" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="Y183" t="n">
@@ -60580,7 +60580,7 @@
       </c>
       <c r="BK183" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="BL183" t="n">
@@ -60677,7 +60677,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>1958-10-17</t>
+          <t>1958-10-25</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -60754,12 +60754,12 @@
       </c>
       <c r="W184" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="X184" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="Y184" t="n">
@@ -60910,7 +60910,7 @@
       </c>
       <c r="BK184" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="BL184" t="n">
@@ -61007,7 +61007,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>1993-11-19</t>
+          <t>1993-11-27</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -61084,12 +61084,12 @@
       </c>
       <c r="W185" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="X185" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="Y185" t="n">
@@ -61240,7 +61240,7 @@
       </c>
       <c r="BK185" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="BL185" t="n">
@@ -61337,7 +61337,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>1997-02-15</t>
+          <t>1997-02-23</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -61414,12 +61414,12 @@
       </c>
       <c r="W186" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="X186" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Y186" t="n">
@@ -61566,7 +61566,7 @@
       </c>
       <c r="BK186" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="BL186" t="n">
@@ -61663,7 +61663,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>1953-01-08</t>
+          <t>1953-01-16</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -61740,12 +61740,12 @@
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="X187" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="Y187" t="n">
@@ -61896,7 +61896,7 @@
       </c>
       <c r="BK187" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="BL187" t="n">
@@ -61993,7 +61993,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>1992-04-20</t>
+          <t>1992-04-28</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -62070,12 +62070,12 @@
       </c>
       <c r="W188" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="X188" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="Y188" t="n">
@@ -62222,7 +62222,7 @@
       </c>
       <c r="BK188" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="BL188" t="n">
@@ -62319,7 +62319,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>1969-07-11</t>
+          <t>1969-07-19</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -62396,12 +62396,12 @@
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="X189" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="Y189" t="n">
@@ -62552,7 +62552,7 @@
       </c>
       <c r="BK189" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-05-04</t>
         </is>
       </c>
       <c r="BL189" t="n">
@@ -62649,7 +62649,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>1995-04-28</t>
+          <t>1995-05-06</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -62726,12 +62726,12 @@
       </c>
       <c r="W190" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="X190" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="Y190" t="n">
@@ -62882,7 +62882,7 @@
       </c>
       <c r="BK190" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="BL190" t="n">
@@ -62979,7 +62979,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>1967-04-19</t>
+          <t>1967-04-27</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -63056,12 +63056,12 @@
       </c>
       <c r="W191" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="X191" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="Y191" t="n">
@@ -63212,7 +63212,7 @@
       </c>
       <c r="BK191" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BL191" t="n">
@@ -63309,7 +63309,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>1993-11-18</t>
+          <t>1993-11-26</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -63386,12 +63386,12 @@
       </c>
       <c r="W192" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="X192" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="Y192" t="n">
@@ -63542,7 +63542,7 @@
       </c>
       <c r="BK192" t="inlineStr">
         <is>
-          <t>2025-07-12</t>
+          <t>2025-07-20</t>
         </is>
       </c>
       <c r="BL192" t="n">
@@ -63639,7 +63639,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>1974-10-30</t>
+          <t>1974-11-07</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -63716,12 +63716,12 @@
       </c>
       <c r="W193" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="X193" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="Y193" t="n">
@@ -63868,7 +63868,7 @@
       </c>
       <c r="BK193" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-06-15</t>
         </is>
       </c>
       <c r="BL193" t="n">
@@ -63965,7 +63965,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>1951-10-17</t>
+          <t>1951-10-25</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -64042,12 +64042,12 @@
       </c>
       <c r="W194" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="X194" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="Y194" t="n">
@@ -64198,7 +64198,7 @@
       </c>
       <c r="BK194" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="BL194" t="n">
@@ -64295,7 +64295,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>1961-10-28</t>
+          <t>1961-11-05</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -64372,12 +64372,12 @@
       </c>
       <c r="W195" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="X195" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Y195" t="n">
@@ -64524,7 +64524,7 @@
       </c>
       <c r="BK195" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="BL195" t="n">
@@ -64621,7 +64621,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>1951-01-08</t>
+          <t>1951-01-16</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -64698,12 +64698,12 @@
       </c>
       <c r="W196" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="X196" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Y196" t="n">
@@ -64850,7 +64850,7 @@
       </c>
       <c r="BK196" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="BL196" t="n">
@@ -64947,7 +64947,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>1958-03-12</t>
+          <t>1958-03-20</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -65024,12 +65024,12 @@
       </c>
       <c r="W197" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="X197" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="Y197" t="n">
@@ -65180,7 +65180,7 @@
       </c>
       <c r="BK197" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="BL197" t="n">
@@ -65277,7 +65277,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>1949-10-18</t>
+          <t>1949-10-26</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -65354,12 +65354,12 @@
       </c>
       <c r="W198" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="X198" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="Y198" t="n">
@@ -65510,7 +65510,7 @@
       </c>
       <c r="BK198" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="BL198" t="n">
@@ -65607,7 +65607,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>1976-08-11</t>
+          <t>1976-08-19</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -65684,12 +65684,12 @@
       </c>
       <c r="W199" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="X199" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="Y199" t="n">
@@ -65840,7 +65840,7 @@
       </c>
       <c r="BK199" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-15</t>
         </is>
       </c>
       <c r="BL199" t="n">
@@ -65937,7 +65937,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>1987-05-18</t>
+          <t>1987-05-26</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -66014,12 +66014,12 @@
       </c>
       <c r="W200" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="X200" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="Y200" t="n">
@@ -66170,7 +66170,7 @@
       </c>
       <c r="BK200" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="BL200" t="n">
@@ -66267,7 +66267,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>1981-04-12</t>
+          <t>1981-04-20</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -66344,12 +66344,12 @@
       </c>
       <c r="W201" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="X201" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Y201" t="n">
@@ -66500,7 +66500,7 @@
       </c>
       <c r="BK201" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="BL201" t="n">
@@ -66597,7 +66597,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>1999-05-12</t>
+          <t>1999-05-20</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -66674,12 +66674,12 @@
       </c>
       <c r="W202" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="X202" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Y202" t="n">
@@ -66830,7 +66830,7 @@
       </c>
       <c r="BK202" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="BL202" t="n">
@@ -66927,7 +66927,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>1964-02-14</t>
+          <t>1964-02-22</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -67004,12 +67004,12 @@
       </c>
       <c r="W203" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="X203" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="Y203" t="n">
@@ -67156,7 +67156,7 @@
       </c>
       <c r="BK203" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="BL203" t="n">
@@ -67253,7 +67253,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>1983-10-03</t>
+          <t>1983-10-11</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -67330,12 +67330,12 @@
       </c>
       <c r="W204" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="X204" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="Y204" t="n">
@@ -67486,7 +67486,7 @@
       </c>
       <c r="BK204" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="BL204" t="n">
@@ -67583,7 +67583,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>1958-09-15</t>
+          <t>1958-09-23</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -67660,12 +67660,12 @@
       </c>
       <c r="W205" t="inlineStr">
         <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
           <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="X205" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
         </is>
       </c>
       <c r="Y205" t="n">
@@ -67816,7 +67816,7 @@
       </c>
       <c r="BK205" t="inlineStr">
         <is>
-          <t>2026-01-18</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="BL205" t="n">
@@ -67913,7 +67913,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>1998-07-30</t>
+          <t>1998-08-07</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -67990,12 +67990,12 @@
       </c>
       <c r="W206" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="X206" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="Y206" t="n">
@@ -68142,7 +68142,7 @@
       </c>
       <c r="BK206" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="BL206" t="n">
@@ -68239,7 +68239,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>1960-01-09</t>
+          <t>1960-01-17</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -68316,12 +68316,12 @@
       </c>
       <c r="W207" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="X207" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="Y207" t="n">
@@ -68468,7 +68468,7 @@
       </c>
       <c r="BK207" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="BL207" t="n">
@@ -68565,7 +68565,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>1940-08-23</t>
+          <t>1940-08-31</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -68642,12 +68642,12 @@
       </c>
       <c r="W208" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="X208" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="Y208" t="n">
@@ -68798,7 +68798,7 @@
       </c>
       <c r="BK208" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="BL208" t="n">
@@ -68895,7 +68895,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>1958-07-20</t>
+          <t>1958-07-28</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -68972,12 +68972,12 @@
       </c>
       <c r="W209" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="X209" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="Y209" t="n">
@@ -69124,7 +69124,7 @@
       </c>
       <c r="BK209" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="BL209" t="n">
@@ -69221,7 +69221,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>1991-05-13</t>
+          <t>1991-05-21</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -69298,12 +69298,12 @@
       </c>
       <c r="W210" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="X210" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="Y210" t="n">
@@ -69450,7 +69450,7 @@
       </c>
       <c r="BK210" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="BL210" t="n">
@@ -69547,7 +69547,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>1942-08-15</t>
+          <t>1942-08-23</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -69624,12 +69624,12 @@
       </c>
       <c r="W211" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="X211" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="Y211" t="n">
@@ -69780,7 +69780,7 @@
       </c>
       <c r="BK211" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="BL211" t="n">
@@ -69877,7 +69877,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>1988-02-27</t>
+          <t>1988-03-06</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -69954,12 +69954,12 @@
       </c>
       <c r="W212" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="X212" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="Y212" t="n">
@@ -70106,7 +70106,7 @@
       </c>
       <c r="BK212" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="BL212" t="n">
@@ -70203,7 +70203,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>1961-01-29</t>
+          <t>1961-02-06</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -70280,12 +70280,12 @@
       </c>
       <c r="W213" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="X213" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="Y213" t="n">
@@ -70436,7 +70436,7 @@
       </c>
       <c r="BK213" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="BL213" t="n">
@@ -70533,7 +70533,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>1973-11-01</t>
+          <t>1973-11-09</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -70610,12 +70610,12 @@
       </c>
       <c r="W214" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="X214" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="Y214" t="n">
@@ -70766,7 +70766,7 @@
       </c>
       <c r="BK214" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="BL214" t="n">
@@ -70863,7 +70863,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>1988-11-27</t>
+          <t>1988-12-05</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -70940,12 +70940,12 @@
       </c>
       <c r="W215" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="X215" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="Y215" t="n">
@@ -71092,7 +71092,7 @@
       </c>
       <c r="BK215" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="BL215" t="n">
@@ -71189,7 +71189,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>1955-12-04</t>
+          <t>1955-12-12</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -71266,12 +71266,12 @@
       </c>
       <c r="W216" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="X216" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="Y216" t="n">
@@ -71418,7 +71418,7 @@
       </c>
       <c r="BK216" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="BL216" t="n">
@@ -71515,7 +71515,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>2001-04-01</t>
+          <t>2001-04-09</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -71592,12 +71592,12 @@
       </c>
       <c r="W217" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="X217" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Y217" t="n">
@@ -71748,7 +71748,7 @@
       </c>
       <c r="BK217" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="BL217" t="n">
@@ -71845,7 +71845,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>1973-03-31</t>
+          <t>1973-04-08</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -71922,12 +71922,12 @@
       </c>
       <c r="W218" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="X218" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="Y218" t="n">
@@ -72074,7 +72074,7 @@
       </c>
       <c r="BK218" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="BL218" t="n">
@@ -72171,7 +72171,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>1993-03-24</t>
+          <t>1993-04-01</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -72248,12 +72248,12 @@
       </c>
       <c r="W219" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="X219" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="Y219" t="n">
@@ -72400,7 +72400,7 @@
       </c>
       <c r="BK219" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="BL219" t="n">
@@ -72497,7 +72497,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>1978-08-14</t>
+          <t>1978-08-22</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -72574,12 +72574,12 @@
       </c>
       <c r="W220" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="X220" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="Y220" t="n">
@@ -72726,7 +72726,7 @@
       </c>
       <c r="BK220" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="BL220" t="n">
@@ -72823,7 +72823,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>1995-06-11</t>
+          <t>1995-06-19</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -72900,12 +72900,12 @@
       </c>
       <c r="W221" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="X221" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="Y221" t="n">
@@ -73052,7 +73052,7 @@
       </c>
       <c r="BK221" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="BL221" t="n">
@@ -73149,7 +73149,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>1942-03-02</t>
+          <t>1942-03-10</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -73226,12 +73226,12 @@
       </c>
       <c r="W222" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="X222" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Y222" t="n">
@@ -73378,7 +73378,7 @@
       </c>
       <c r="BK222" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BL222" t="n">
@@ -73475,7 +73475,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>1967-10-27</t>
+          <t>1967-11-04</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -73552,12 +73552,12 @@
       </c>
       <c r="W223" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="X223" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="Y223" t="n">
@@ -73708,7 +73708,7 @@
       </c>
       <c r="BK223" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="BL223" t="n">
@@ -73805,7 +73805,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>1987-04-28</t>
+          <t>1987-05-06</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -73882,12 +73882,12 @@
       </c>
       <c r="W224" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="X224" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="Y224" t="n">
@@ -74038,7 +74038,7 @@
       </c>
       <c r="BK224" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="BL224" t="n">
@@ -74135,7 +74135,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>1987-01-09</t>
+          <t>1987-01-17</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -74212,12 +74212,12 @@
       </c>
       <c r="W225" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="X225" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="Y225" t="n">
@@ -74364,7 +74364,7 @@
       </c>
       <c r="BK225" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="BL225" t="n">
@@ -74461,7 +74461,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>1984-04-12</t>
+          <t>1984-04-20</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -74538,12 +74538,12 @@
       </c>
       <c r="W226" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="X226" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="Y226" t="n">
@@ -74690,7 +74690,7 @@
       </c>
       <c r="BK226" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-09</t>
         </is>
       </c>
       <c r="BL226" t="n">
@@ -74787,7 +74787,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>1991-11-18</t>
+          <t>1991-11-26</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -74864,12 +74864,12 @@
       </c>
       <c r="W227" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="X227" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2026-01-04</t>
         </is>
       </c>
       <c r="Y227" t="n">
@@ -75020,7 +75020,7 @@
       </c>
       <c r="BK227" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="BL227" t="n">
@@ -75117,7 +75117,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>1997-09-14</t>
+          <t>1997-09-22</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -75194,12 +75194,12 @@
       </c>
       <c r="W228" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="X228" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="Y228" t="n">
@@ -75346,7 +75346,7 @@
       </c>
       <c r="BK228" t="inlineStr">
         <is>
-          <t>2025-05-24</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="BL228" t="n">
@@ -75443,7 +75443,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>1948-07-21</t>
+          <t>1948-07-29</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -75520,12 +75520,12 @@
       </c>
       <c r="W229" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="X229" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="Y229" t="n">
@@ -75672,7 +75672,7 @@
       </c>
       <c r="BK229" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="BL229" t="n">
@@ -75769,7 +75769,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>1966-03-20</t>
+          <t>1966-03-28</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -75846,12 +75846,12 @@
       </c>
       <c r="W230" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="X230" t="inlineStr">
         <is>
-          <t>2025-12-25</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="Y230" t="n">
@@ -75998,7 +75998,7 @@
       </c>
       <c r="BK230" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="BL230" t="n">
@@ -76095,7 +76095,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>1969-02-24</t>
+          <t>1969-03-04</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -76172,12 +76172,12 @@
       </c>
       <c r="W231" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="X231" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="Y231" t="n">
@@ -76328,7 +76328,7 @@
       </c>
       <c r="BK231" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="BL231" t="n">
@@ -76425,7 +76425,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>1966-06-12</t>
+          <t>1966-06-20</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -76502,12 +76502,12 @@
       </c>
       <c r="W232" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="X232" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="Y232" t="n">
@@ -76654,7 +76654,7 @@
       </c>
       <c r="BK232" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="BL232" t="n">
@@ -76751,7 +76751,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>1955-08-06</t>
+          <t>1955-08-14</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -76828,12 +76828,12 @@
       </c>
       <c r="W233" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="X233" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Y233" t="n">
@@ -76980,7 +76980,7 @@
       </c>
       <c r="BK233" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="BL233" t="n">
@@ -77077,7 +77077,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>1960-07-18</t>
+          <t>1960-07-26</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -77154,12 +77154,12 @@
       </c>
       <c r="W234" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="X234" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="Y234" t="n">
@@ -77310,7 +77310,7 @@
       </c>
       <c r="BK234" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="BL234" t="n">
@@ -77407,7 +77407,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>1969-10-06</t>
+          <t>1969-10-14</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -77484,12 +77484,12 @@
       </c>
       <c r="W235" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="X235" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="Y235" t="n">
@@ -77640,7 +77640,7 @@
       </c>
       <c r="BK235" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="BL235" t="n">
@@ -77737,7 +77737,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>1941-09-28</t>
+          <t>1941-10-06</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -77814,12 +77814,12 @@
       </c>
       <c r="W236" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="X236" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Y236" t="n">
@@ -77966,7 +77966,7 @@
       </c>
       <c r="BK236" t="inlineStr">
         <is>
-          <t>2025-10-18</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="BL236" t="n">
@@ -78063,7 +78063,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>1948-01-22</t>
+          <t>1948-01-30</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -78140,12 +78140,12 @@
       </c>
       <c r="W237" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="X237" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="Y237" t="n">
@@ -78296,7 +78296,7 @@
       </c>
       <c r="BK237" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="BL237" t="n">
@@ -78393,7 +78393,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>2001-02-06</t>
+          <t>2001-02-14</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -78470,12 +78470,12 @@
       </c>
       <c r="W238" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="X238" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="Y238" t="n">
@@ -78622,7 +78622,7 @@
       </c>
       <c r="BK238" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="BL238" t="n">
@@ -78719,7 +78719,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>1976-04-17</t>
+          <t>1976-04-25</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -78796,12 +78796,12 @@
       </c>
       <c r="W239" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="X239" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Y239" t="n">
@@ -78952,7 +78952,7 @@
       </c>
       <c r="BK239" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="BL239" t="n">
@@ -79049,7 +79049,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>1982-04-05</t>
+          <t>1982-04-13</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -79126,12 +79126,12 @@
       </c>
       <c r="W240" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="X240" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="Y240" t="n">
@@ -79278,7 +79278,7 @@
       </c>
       <c r="BK240" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="BL240" t="n">
@@ -79375,7 +79375,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>1965-05-13</t>
+          <t>1965-05-21</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -79452,12 +79452,12 @@
       </c>
       <c r="W241" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="X241" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="Y241" t="n">
@@ -79608,7 +79608,7 @@
       </c>
       <c r="BK241" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-01-18</t>
         </is>
       </c>
       <c r="BL241" t="n">
@@ -79705,7 +79705,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>1968-08-16</t>
+          <t>1968-08-24</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -79782,12 +79782,12 @@
       </c>
       <c r="W242" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="X242" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="Y242" t="n">
@@ -79938,7 +79938,7 @@
       </c>
       <c r="BK242" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="BL242" t="n">
@@ -80035,7 +80035,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>1949-01-09</t>
+          <t>1949-01-17</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -80112,12 +80112,12 @@
       </c>
       <c r="W243" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="X243" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2026-01-11</t>
         </is>
       </c>
       <c r="Y243" t="n">
@@ -80264,7 +80264,7 @@
       </c>
       <c r="BK243" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="BL243" t="n">
@@ -80361,7 +80361,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>1995-08-01</t>
+          <t>1995-08-09</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -80438,12 +80438,12 @@
       </c>
       <c r="W244" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="X244" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="Y244" t="n">
@@ -80594,7 +80594,7 @@
       </c>
       <c r="BK244" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="BL244" t="n">
@@ -80691,7 +80691,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>1996-09-10</t>
+          <t>1996-09-18</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -80768,12 +80768,12 @@
       </c>
       <c r="W245" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="X245" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="Y245" t="n">
@@ -80924,7 +80924,7 @@
       </c>
       <c r="BK245" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="BL245" t="n">
@@ -81021,7 +81021,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>1971-01-10</t>
+          <t>1971-01-18</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -81098,12 +81098,12 @@
       </c>
       <c r="W246" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="X246" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="Y246" t="n">
@@ -81254,7 +81254,7 @@
       </c>
       <c r="BK246" t="inlineStr">
         <is>
-          <t>2026-01-24</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="BL246" t="n">
@@ -81351,7 +81351,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>1952-08-26</t>
+          <t>1952-09-03</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -81428,12 +81428,12 @@
       </c>
       <c r="W247" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="X247" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Y247" t="n">
@@ -81580,7 +81580,7 @@
       </c>
       <c r="BK247" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="BL247" t="n">
@@ -81677,7 +81677,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>1970-03-12</t>
+          <t>1970-03-20</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -81754,12 +81754,12 @@
       </c>
       <c r="W248" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="X248" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="Y248" t="n">
@@ -81910,7 +81910,7 @@
       </c>
       <c r="BK248" t="inlineStr">
         <is>
-          <t>2025-06-21</t>
+          <t>2025-06-29</t>
         </is>
       </c>
       <c r="BL248" t="n">
@@ -82007,7 +82007,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>1955-04-18</t>
+          <t>1955-04-26</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -82084,12 +82084,12 @@
       </c>
       <c r="W249" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="X249" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="Y249" t="n">
@@ -82240,7 +82240,7 @@
       </c>
       <c r="BK249" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="BL249" t="n">
@@ -82337,7 +82337,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>1965-09-25</t>
+          <t>1965-10-03</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -82414,12 +82414,12 @@
       </c>
       <c r="W250" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="X250" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="Y250" t="n">
@@ -82570,7 +82570,7 @@
       </c>
       <c r="BK250" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="BL250" t="n">
@@ -82667,7 +82667,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>1943-10-16</t>
+          <t>1943-10-24</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -82744,12 +82744,12 @@
       </c>
       <c r="W251" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="X251" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="Y251" t="n">
@@ -82900,7 +82900,7 @@
       </c>
       <c r="BK251" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="BL251" t="n">
